--- a/www/download/IND.abstract_labour.empe.s.mv.rpO1.xlsx
+++ b/www/download/IND.abstract_labour.empe.s.mv.rpO1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15270423.144</t>
+          <t>15270423144280.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14979405.228</t>
+          <t>14979405228456.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14841365.767</t>
+          <t>14841365767243</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14728354.932</t>
+          <t>14728354931841.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>17484220.563</t>
+          <t>17484220563302</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>18622927.487</t>
+          <t>18622927487486.3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18058210.885</t>
+          <t>18058210884843.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19530004.439</t>
+          <t>19530004439180.2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>24336282.859</t>
+          <t>24336282858513.6</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23774752.656</t>
+          <t>23774752656221.2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>23786034.573</t>
+          <t>23786034572552.3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>21544350.591</t>
+          <t>21544350590767.5</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>19017444.615</t>
+          <t>19017444614570.2</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>15336831.318</t>
+          <t>15336831317859</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>14232994.696</t>
+          <t>14232994695963.1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10293939.797</t>
+          <t>10293939796682.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8622738.4</t>
+          <t>8622738400333.97</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7614459.545</t>
+          <t>7614459544742.49</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8591732.047</t>
+          <t>8591732047484.02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9352610.163</t>
+          <t>9352610162870.8</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9300852.285</t>
+          <t>9300852284665.88</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9551552.933</t>
+          <t>9551552932521.1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10012496.85</t>
+          <t>10012496849726.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>11938087.244</t>
+          <t>11938087243740.6</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>10740405.995</t>
+          <t>10740405994617.8</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>9968285.518</t>
+          <t>9968285517648.39</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>8834505.383</t>
+          <t>8834505382873.64</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>7419533.055</t>
+          <t>7419533054562.6</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>6137311.689</t>
+          <t>6137311688509.41</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>5545137.538</t>
+          <t>5545137538025.44</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11725146.186</t>
+          <t>11725146186067</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9878405.068</t>
+          <t>9878405068291.05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8907022.946</t>
+          <t>8907022945631.19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10032072.167</t>
+          <t>10032072166913.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>11106105.672</t>
+          <t>11106105671758.7</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11180422.424</t>
+          <t>11180422423614.9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11899028.104</t>
+          <t>11899028103913.1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>12734490.861</t>
+          <t>12734490861367.2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>15137634.459</t>
+          <t>15137634459165.6</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>13722627.615</t>
+          <t>13722627615448.1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>12706374.619</t>
+          <t>12706374618661.2</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>11259615.352</t>
+          <t>11259615351886</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>9466077.357</t>
+          <t>9466077356840.28</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>7803971.225</t>
+          <t>7803971225002.63</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>7114536.661</t>
+          <t>7114536660547.33</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>441497.541</t>
+          <t>441497541117.697</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>350565.566</t>
+          <t>350565566075.13</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>265083.592</t>
+          <t>265083591821.253</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>382354.34</t>
+          <t>382354339971.123</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>407426.509</t>
+          <t>407426509126.75</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>412859.125</t>
+          <t>412859124576.126</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>466171.394</t>
+          <t>466171393598.625</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>510166.224</t>
+          <t>510166224313.686</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>649237.852</t>
+          <t>649237852298.534</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>618380.149</t>
+          <t>618380149303.893</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>608427.307</t>
+          <t>608427307260.299</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>570854.188</t>
+          <t>570854187701.533</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>550844.067</t>
+          <t>550844066571.727</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>520492.383</t>
+          <t>520492383459.036</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>498645.001</t>
+          <t>498645000965.344</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>26381617.874</t>
+          <t>26381617873835.9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24999450.579</t>
+          <t>24999450578998.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25194271.276</t>
+          <t>25194271276350.8</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>27402945.386</t>
+          <t>27402945386418.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20639044.739</t>
+          <t>20639044738503.7</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>24622181.197</t>
+          <t>24622181196805.1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>22176053.379</t>
+          <t>22176053378571</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19894866.454</t>
+          <t>19894866453613.5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>20498070.741</t>
+          <t>20498070740815.1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>19566740.017</t>
+          <t>19566740017382.4</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>23812144.746</t>
+          <t>23812144745849.8</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>25057711.754</t>
+          <t>25057711753844.6</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>23251544.008</t>
+          <t>23251544008021</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>20744109.363</t>
+          <t>20744109362951.3</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>20169821.373</t>
+          <t>20169821372800.3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24541156.906</t>
+          <t>24541156906393.1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>22016046.296</t>
+          <t>22016046296277.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22938657.728</t>
+          <t>22938657728367.3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24825105.64</t>
+          <t>24825105640009.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>28762246.696</t>
+          <t>28762246695817.3</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34653403.271</t>
+          <t>34653403270824.4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>36118184.116</t>
+          <t>36118184115847.9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>36226337.235</t>
+          <t>36226337234733.5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>41559122.622</t>
+          <t>41559122621708.6</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>37948257.494</t>
+          <t>37948257494024.3</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>38547604.175</t>
+          <t>38547604174655.5</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>36877893.246</t>
+          <t>36877893245805.1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>30017710.804</t>
+          <t>30017710803501.3</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>23407507.248</t>
+          <t>23407507247880.4</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>19746594.046</t>
+          <t>19746594045920.3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>31998102.2</t>
+          <t>31998102199604.6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>32748668.258</t>
+          <t>32748668257585.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>36117873.751</t>
+          <t>36117873750611.7</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41949641.258</t>
+          <t>41949641258056.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>47877327.337</t>
+          <t>47877327336647.5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>57294572.958</t>
+          <t>57294572957963</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>64561106.583</t>
+          <t>64561106582631.3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>67644556.255</t>
+          <t>67644556254672.3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>72509174.318</t>
+          <t>72509174317982.7</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>67385913.696</t>
+          <t>67385913695807.2</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>68275917.671</t>
+          <t>68275917670928.2</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>66474810.413</t>
+          <t>66474810413069.6</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>60451586.261</t>
+          <t>60451586260903.6</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>57184219.843</t>
+          <t>57184219843445.7</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>59590153.227</t>
+          <t>59590153226835.9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>322453.385</t>
+          <t>322453385225.373</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>287811.839</t>
+          <t>287811839158.296</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>279054.161</t>
+          <t>279054160545.019</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>321671.836</t>
+          <t>321671835715.515</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>358893.934</t>
+          <t>358893933833.707</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>374911.876</t>
+          <t>374911876090.507</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>401193.822</t>
+          <t>401193821735.331</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>446036.43</t>
+          <t>446036430189.409</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>568672.767</t>
+          <t>568672766574.176</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>534197.002</t>
+          <t>534197001745.29</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>512157.462</t>
+          <t>512157461982.151</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>463667.946</t>
+          <t>463667946426.819</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>392885.966</t>
+          <t>392885965865.128</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>330799.139</t>
+          <t>330799138749.05</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>302656.969</t>
+          <t>302656968943.812</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1465417.853</t>
+          <t>1465417852856.52</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1903539.214</t>
+          <t>1903539214075.86</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1769289.079</t>
+          <t>1769289079269.11</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2020130.12</t>
+          <t>2020130120373.78</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2136634.966</t>
+          <t>2136634965952.91</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2251126.129</t>
+          <t>2251126129225.55</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2563809.136</t>
+          <t>2563809135935.91</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3123678.279</t>
+          <t>3123678278841.68</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>3740490.016</t>
+          <t>3740490015508.88</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>3509401.957</t>
+          <t>3509401957400.53</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3599053.273</t>
+          <t>3599053273328.18</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>3455383.59</t>
+          <t>3455383590064.45</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>3086208.459</t>
+          <t>3086208459202.86</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2873118.076</t>
+          <t>2873118076375.32</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2369106.037</t>
+          <t>2369106036593.68</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>109641515.518</t>
+          <t>109641515517843</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>91730143.881</t>
+          <t>91730143881314.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80034122.552</t>
+          <t>80034122552153.3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>88952660.801</t>
+          <t>88952660800828.4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>96005449.949</t>
+          <t>96005449948777.9</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>95898150.695</t>
+          <t>95898150694713.6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>98463011.861</t>
+          <t>98463011861145.1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>102140717.004</t>
+          <t>102140717004040</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>119598687.918</t>
+          <t>119598687918136</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>105961349.687</t>
+          <t>105961349686898</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>94314849.723</t>
+          <t>94314849723252.8</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>81177889.905</t>
+          <t>81177889904861</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>66585084.543</t>
+          <t>66585084542783</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>54291272.075</t>
+          <t>54291272075496.1</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>49510066.484</t>
+          <t>49510066483948.1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7638203.548</t>
+          <t>7638203548280.43</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6765622.712</t>
+          <t>6765622711757.37</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6236508.677</t>
+          <t>6236508677310.63</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7187017.284</t>
+          <t>7187017283740.27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7948603.077</t>
+          <t>7948603076879.29</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7955862.188</t>
+          <t>7955862188445.5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8445745.97</t>
+          <t>8445745970221.06</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9025016.575</t>
+          <t>9025016575474.79</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>10818425.162</t>
+          <t>10818425161697.5</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9825622.457</t>
+          <t>9825622457378.73</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9223377.744</t>
+          <t>9223377744467.86</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>8246267.386</t>
+          <t>8246267386496.31</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>7036162.577</t>
+          <t>7036162576947.81</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>5786768.523</t>
+          <t>5786768523205.19</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>5261983.055</t>
+          <t>5261983055043.51</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>23469067.314</t>
+          <t>23469067314145.8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21364281.289</t>
+          <t>21364281288854.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19932327.173</t>
+          <t>19932327172838.7</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>23039929.907</t>
+          <t>23039929906501.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>26011072.576</t>
+          <t>26011072575565.6</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>27174537.795</t>
+          <t>27174537794582</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>29367021.412</t>
+          <t>29367021411835.4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>32123133.853</t>
+          <t>32123133853178.5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>39954639.856</t>
+          <t>39954639855582</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>37354265.094</t>
+          <t>37354265094313.3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>35932453.164</t>
+          <t>35932453164025.9</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>32798186.102</t>
+          <t>32798186102470.1</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>28327782.28</t>
+          <t>28327782279822.3</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>23501977.525</t>
+          <t>23501977524873.9</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>20751412.602</t>
+          <t>20751412602112.4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>159097.893</t>
+          <t>159097893010.544</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>165392.192</t>
+          <t>165392191506.35</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>171035.076</t>
+          <t>171035076418.856</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>206041.671</t>
+          <t>206041671242.349</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>224849.723</t>
+          <t>224849722867.804</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>242776.758</t>
+          <t>242776758444.949</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>271526.785</t>
+          <t>271526784932.499</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>310648.298</t>
+          <t>310648298435.122</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>407375.592</t>
+          <t>407375592305.895</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>399517.654</t>
+          <t>399517654406.981</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>412354.585</t>
+          <t>412354584697.934</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>419431.367</t>
+          <t>419431366904.086</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>415624.7</t>
+          <t>415624699836.783</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>369349.318</t>
+          <t>369349318113.02</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>294325.026</t>
+          <t>294325026441.586</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5210029.054</t>
+          <t>5210029053626.28</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4489267.289</t>
+          <t>4489267288631.03</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4189899.581</t>
+          <t>4189899580705.81</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4832934.005</t>
+          <t>4832934004852.93</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5315516.64</t>
+          <t>5315516639866.31</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5430537.714</t>
+          <t>5430537713968</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5831078.801</t>
+          <t>5831078800667</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6189242.258</t>
+          <t>6189242258198.54</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7433848.358</t>
+          <t>7433848357978.66</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>6826455.58</t>
+          <t>6826455579593.23</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>6433666.572</t>
+          <t>6433666572061.72</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>5693374.479</t>
+          <t>5693374478634.85</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>4820295.533</t>
+          <t>4820295533223.71</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>4020053.646</t>
+          <t>4020053645979.07</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3605817.239</t>
+          <t>3605817239051.18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>65501715.579</t>
+          <t>65501715578833.5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>57152499.622</t>
+          <t>57152499621564.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>51450329.193</t>
+          <t>51450329193333.6</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>58325467.285</t>
+          <t>58325467285363.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>64149181.6</t>
+          <t>64149181599947.6</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>65084626.534</t>
+          <t>65084626533764.7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>68570693.827</t>
+          <t>68570693826570.8</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>73582800.992</t>
+          <t>73582800991590.6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>88391702.195</t>
+          <t>88391702195039.4</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>80712935.273</t>
+          <t>80712935272816</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>74921606.846</t>
+          <t>74921606846019.6</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>66149047.517</t>
+          <t>66149047517227.7</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>54958205.879</t>
+          <t>54958205879381</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>44579007.132</t>
+          <t>44579007131523.7</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>40182232.353</t>
+          <t>40182232352505</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>49007345.312</t>
+          <t>49007345311986.8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44164060.904</t>
+          <t>44164060903634.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>49307163.785</t>
+          <t>49307163785366.1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>59693240.769</t>
+          <t>59693240769182</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>68123345.223</t>
+          <t>68123345223347.2</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>76044384.386</t>
+          <t>76044384386223.9</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>79590257.404</t>
+          <t>79590257404258.4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>84323734.198</t>
+          <t>84323734198176.8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>94070226.091</t>
+          <t>94070226091230.1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>88967882.309</t>
+          <t>88967882309291.1</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>83548522.485</t>
+          <t>83548522485408.6</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>74625157.543</t>
+          <t>74625157542974.6</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>62575829.021</t>
+          <t>62575829021353.2</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>43196992.454</t>
+          <t>43196992453596.4</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>34902210.341</t>
+          <t>34902210340739.3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3378964.463</t>
+          <t>3378964462542.32</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3078287.254</t>
+          <t>3078287253602.58</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3087613.763</t>
+          <t>3087613762613.07</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3476786.249</t>
+          <t>3476786249002.59</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4011294.913</t>
+          <t>4011294913006.69</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3997072.576</t>
+          <t>3997072575628.96</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4200368.38</t>
+          <t>4200368380301.95</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5006628.201</t>
+          <t>5006628201389.15</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>6331358.533</t>
+          <t>6331358532561.2</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>6039538.49</t>
+          <t>6039538489704.67</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>5720908.346</t>
+          <t>5720908345959.06</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>5212382.529</t>
+          <t>5212382529192.48</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>4534900.574</t>
+          <t>4534900574281.13</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3823871.537</t>
+          <t>3823871536958.4</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3573694.658</t>
+          <t>3573694657597.26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1700913.671</t>
+          <t>1700913671240.09</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1456604.196</t>
+          <t>1456604195524.18</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1463262.594</t>
+          <t>1463262594119.15</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1652763.836</t>
+          <t>1652763835509.8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1786710.485</t>
+          <t>1786710485337.57</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1970168.215</t>
+          <t>1970168214604.26</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2338071.076</t>
+          <t>2338071076183.82</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2900406.618</t>
+          <t>2900406618495.95</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3613602.567</t>
+          <t>3613602567473.04</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3516110.732</t>
+          <t>3516110732275.34</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3453061.075</t>
+          <t>3453061074854.67</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2929416.484</t>
+          <t>2929416483861.01</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2627471.749</t>
+          <t>2627471748832.43</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2156338.612</t>
+          <t>2156338611804.47</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1675195.417</t>
+          <t>1675195417273.43</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6006713.016</t>
+          <t>6006713015930.48</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6005229.602</t>
+          <t>6005229601963.72</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5984584.246</t>
+          <t>5984584245557.31</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2503087.519</t>
+          <t>2503087518548.83</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4164301.67</t>
+          <t>4164301670186.51</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4917005.377</t>
+          <t>4917005376947.16</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5008828.449</t>
+          <t>5008828449028.24</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>5931780.186</t>
+          <t>5931780186483.05</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6966346.747</t>
+          <t>6966346747199.37</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>5905716.685</t>
+          <t>5905716684918.94</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>5769663.735</t>
+          <t>5769663734656.23</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>6454709.619</t>
+          <t>6454709619449.18</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>5576144.877</t>
+          <t>5576144877174.34</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>4793842.553</t>
+          <t>4793842552687.14</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>4865522.656</t>
+          <t>4865522655818.79</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9941780.385</t>
+          <t>9941780384902.62</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8405401.096</t>
+          <t>8405401095594.81</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>9756990.473</t>
+          <t>9756990473014.23</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>10805833.747</t>
+          <t>10805833746704.2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>12403393.43</t>
+          <t>12403393429829.4</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>13995293.147</t>
+          <t>13995293146965.1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>14951257.255</t>
+          <t>14951257254813.7</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>15079550.675</t>
+          <t>15079550675012.8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>17024763.827</t>
+          <t>17024763826599.5</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>15751823.564</t>
+          <t>15751823564132.3</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>16433721.431</t>
+          <t>16433721430591.2</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>15339419.618</t>
+          <t>15339419617816.8</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>13887885.355</t>
+          <t>13887885355042.6</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>11057512.518</t>
+          <t>11057512517747.6</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>11031305.655</t>
+          <t>11031305654966.3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2430220.011</t>
+          <t>2430220010556.97</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2300650.41</t>
+          <t>2300650409830.41</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2431933.348</t>
+          <t>2431933347817.31</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2855358.379</t>
+          <t>2855358379289.75</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3331103.28</t>
+          <t>3331103279697.14</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3645323.901</t>
+          <t>3645323901112.19</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4093859.126</t>
+          <t>4093859125742.56</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4522467.618</t>
+          <t>4522467617787.27</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>5706100.993</t>
+          <t>5706100992751.53</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>5480439.918</t>
+          <t>5480439917760.73</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>5509209.548</t>
+          <t>5509209548142.66</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>5133715.322</t>
+          <t>5133715322298.08</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>4442407.26</t>
+          <t>4442407259876.91</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>3712240.08</t>
+          <t>3712240080101.58</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>3052190.019</t>
+          <t>3052190018972.5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>37425634.969</t>
+          <t>37425634969100.1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>36512819.018</t>
+          <t>36512819018002.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>34752632.811</t>
+          <t>34752632810952.5</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>37380730.106</t>
+          <t>37380730106051.8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>40574639.271</t>
+          <t>40574639271203.8</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>40685969.174</t>
+          <t>40685969173970.7</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>43281452.163</t>
+          <t>43281452162737.8</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>46658242.766</t>
+          <t>46658242766373.3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>56595578.469</t>
+          <t>56595578468728.8</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>51731902.206</t>
+          <t>51731902206129.8</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>48539803.148</t>
+          <t>48539803147560.8</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>42987226.627</t>
+          <t>42987226626731.8</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>35687763.35</t>
+          <t>35687763350282.8</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>29041174.73</t>
+          <t>29041174730386.2</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>26056974.887</t>
+          <t>26056974887012.7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>220802206.541</t>
+          <t>220802206541266</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>164988174.591</t>
+          <t>164988174591111</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>150915984.908</t>
+          <t>150915984907632</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>152147982.479</t>
+          <t>152147982478501</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>187409122.803</t>
+          <t>187409122803240</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>222006232.312</t>
+          <t>222006232311545</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>202793513.566</t>
+          <t>202793513565962</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>187126048.465</t>
+          <t>187126048464519</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>195254920.882</t>
+          <t>195254920882370</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>170165381.115</t>
+          <t>170165381114901</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>150841216.12</t>
+          <t>150841216119689</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>122661080.516</t>
+          <t>122661080516037</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>89898285.835</t>
+          <t>89898285834821.2</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>72830848.078</t>
+          <t>72830848078227.4</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>70435624.228</t>
+          <t>70435624227573.1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20035078.482</t>
+          <t>20035078481851.4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19072042.144</t>
+          <t>19072042144130.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17479043.687</t>
+          <t>17479043687391.6</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>12474509.107</t>
+          <t>12474509106876.1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17036743.428</t>
+          <t>17036743427872</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>21610343.199</t>
+          <t>21610343199190.1</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21549294.307</t>
+          <t>21549294307486.2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>23976495.678</t>
+          <t>23976495677623.6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>26868724.541</t>
+          <t>26868724541010.9</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>24147804.672</t>
+          <t>24147804672358.3</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>25987288.093</t>
+          <t>25987288093318.8</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>24757682.697</t>
+          <t>24757682697051.2</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>19908039.776</t>
+          <t>19908039775930.6</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>13186145.88</t>
+          <t>13186145879955.2</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>11147767.592</t>
+          <t>11147767592115.5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>201333.203</t>
+          <t>201333203133.024</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>222880.013</t>
+          <t>222880012705.667</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>273910.622</t>
+          <t>273910622205.164</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>361442.312</t>
+          <t>361442311940.14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>399732.176</t>
+          <t>399732175667.57</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>424904.691</t>
+          <t>424904691035.641</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>453720.727</t>
+          <t>453720727377.006</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>523348.469</t>
+          <t>523348468507.868</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>679297.256</t>
+          <t>679297256070.24</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>680272.869</t>
+          <t>680272869483.613</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>712042.009</t>
+          <t>712042009285.929</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>725626.571</t>
+          <t>725626571343.292</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>695077.855</t>
+          <t>695077854716.585</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>639868.164</t>
+          <t>639868164408.035</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>476133.368</t>
+          <t>476133368207.203</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>783363.66</t>
+          <t>783363660443.819</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>678243.173</t>
+          <t>678243173272.074</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>622431.419</t>
+          <t>622431419176.78</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>716010.466</t>
+          <t>716010466480.356</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>824291.04</t>
+          <t>824291039616.284</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>884424.232</t>
+          <t>884424232342.424</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>977216.129</t>
+          <t>977216129367.34</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1072703.118</t>
+          <t>1072703117795.65</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1290617.142</t>
+          <t>1290617142232.72</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1204708.618</t>
+          <t>1204708617630.17</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1163055.802</t>
+          <t>1163055801866.89</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1049031.083</t>
+          <t>1049031083405.19</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>910199.43</t>
+          <t>910199430182.028</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>821654.877</t>
+          <t>821654877441.064</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>768335.816</t>
+          <t>768335815924.908</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>174705.33</t>
+          <t>174705329678.288</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>182516.942</t>
+          <t>182516942205.561</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>192397.097</t>
+          <t>192397096539.825</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>227735.314</t>
+          <t>227735313539.032</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>269578.234</t>
+          <t>269578234474.19</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>304746.315</t>
+          <t>304746315242.759</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>322443.725</t>
+          <t>322443725285.322</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>342348.203</t>
+          <t>342348202967.232</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>412663.327</t>
+          <t>412663327036.971</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>405089.323</t>
+          <t>405089322868.065</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>449620.257</t>
+          <t>449620256984.141</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>491427.255</t>
+          <t>491427254939.056</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>554919.237</t>
+          <t>554919237086.201</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>514378.759</t>
+          <t>514378759051.553</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>342517.452</t>
+          <t>342517452220.959</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>7838006.705</t>
+          <t>7838006704692.7</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7316027.022</t>
+          <t>7316027022056.67</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>9087614.953</t>
+          <t>9087614952784.59</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>10932049.093</t>
+          <t>10932049092942.3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>13897484.777</t>
+          <t>13897484777438.2</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>18711782.521</t>
+          <t>18711782521072.6</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>21588749.289</t>
+          <t>21588749289327.7</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>21988222.878</t>
+          <t>21988222878036.3</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>20512474.999</t>
+          <t>20512474999404.6</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>16855252.902</t>
+          <t>16855252902340.7</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>16793518.178</t>
+          <t>16793518178257.1</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>15250946.667</t>
+          <t>15250946667305</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>11944559.28</t>
+          <t>11944559280313.8</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>9210826.909</t>
+          <t>9210826909091.7</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>7128616.667</t>
+          <t>7128616666987.65</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>129970.731</t>
+          <t>129970731388.305</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>120113.974</t>
+          <t>120113973633.518</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>116752.42</t>
+          <t>116752420215.85</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>135638.465</t>
+          <t>135638464667.137</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>151639.409</t>
+          <t>151639408958.882</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>161017.816</t>
+          <t>161017816270.566</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>175939.005</t>
+          <t>175939005005.319</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>187788.153</t>
+          <t>187788152648.341</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>218421.279</t>
+          <t>218421278582.07</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>198939.851</t>
+          <t>198939850878.752</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>182747.238</t>
+          <t>182747238031.433</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>163657.671</t>
+          <t>163657671095.148</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>137090.363</t>
+          <t>137090363315.219</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>126370.171</t>
+          <t>126370170743.532</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>113296.426</t>
+          <t>113296426157.617</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>17217626.255</t>
+          <t>17217626255045.3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>14815199.115</t>
+          <t>14815199115074.9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13558295.847</t>
+          <t>13558295847314.4</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>15831235.26</t>
+          <t>15831235260130.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>17859020.927</t>
+          <t>17859020926859.2</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>18437191.138</t>
+          <t>18437191138407.8</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>19951082.918</t>
+          <t>19951082918300.5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>21594848.537</t>
+          <t>21594848536870.9</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>25937517.469</t>
+          <t>25937517469273.5</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>23378195.986</t>
+          <t>23378195986412.1</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>21231183.094</t>
+          <t>21231183093774</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>18704330.776</t>
+          <t>18704330776311.4</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>15812060.813</t>
+          <t>15812060813302.4</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>13025738.725</t>
+          <t>13025738725023.8</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>11920798.026</t>
+          <t>11920798025933.7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>4449363.089</t>
+          <t>4449363088985.94</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4498086.642</t>
+          <t>4498086642349.93</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4608703.208</t>
+          <t>4608703208010.43</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>5614579.973</t>
+          <t>5614579972813.75</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>5924665.103</t>
+          <t>5924665102909.88</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6503988.188</t>
+          <t>6503988188051.65</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>7656983.69</t>
+          <t>7656983689599.62</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>7422151.415</t>
+          <t>7422151414651.49</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>7729446.09</t>
+          <t>7729446090128.17</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>6881730.121</t>
+          <t>6881730120708.93</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>7305048.863</t>
+          <t>7305048863190.61</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6829274.764</t>
+          <t>6829274764098.6</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>6241348.997</t>
+          <t>6241348997320.55</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>5983006.281</t>
+          <t>5983006280507.12</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>4531131.299</t>
+          <t>4531131298896.91</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>4384638.768</t>
+          <t>4384638768057.55</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4014056.5</t>
+          <t>4014056499933.1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3857639.936</t>
+          <t>3857639936220.8</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4512061.624</t>
+          <t>4512061624099.17</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>5089663.409</t>
+          <t>5089663409469.37</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5313613.773</t>
+          <t>5313613773030.83</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5648835.247</t>
+          <t>5648835246607.72</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>6119834.997</t>
+          <t>6119834996949.27</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>7330057.024</t>
+          <t>7330057023952.1</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>6687721.141</t>
+          <t>6687721140546.74</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>6285043.317</t>
+          <t>6285043317059.37</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>5650420.068</t>
+          <t>5650420068444.68</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>4691186.004</t>
+          <t>4691186003734.89</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3799543.794</t>
+          <t>3799543794090.85</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>3417881.272</t>
+          <t>3417881272241.4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1148851.051</t>
+          <t>1148851050548.85</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>988451.651</t>
+          <t>988451651159.806</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>818573.795</t>
+          <t>818573794867.751</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1238761.348</t>
+          <t>1238761348362.24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1078054.672</t>
+          <t>1078054671578.94</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1406748.099</t>
+          <t>1406748099303.94</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1651466.523</t>
+          <t>1651466523019.63</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1741238.046</t>
+          <t>1741238045783.9</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2080811.469</t>
+          <t>2080811469249.54</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2100921.446</t>
+          <t>2100921445942.27</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2603118.103</t>
+          <t>2603118102692.84</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2650349.132</t>
+          <t>2650349131607.62</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2737716.215</t>
+          <t>2737716215437.81</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2595208.495</t>
+          <t>2595208494976.43</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1911805.938</t>
+          <t>1911805938063.05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>12157161.94</t>
+          <t>12157161939745.8</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>12976775.735</t>
+          <t>12976775734649.9</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12952517.663</t>
+          <t>12952517663476.1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>10878268.927</t>
+          <t>10878268926614</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6897337.545</t>
+          <t>6897337544722.02</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>9958510.695</t>
+          <t>9958510695268.88</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>12287360.959</t>
+          <t>12287360958622.2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>14126300.075</t>
+          <t>14126300075196.9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>16784551.592</t>
+          <t>16784551592131.3</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>17988939.927</t>
+          <t>17988939926635.8</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>20267785.774</t>
+          <t>20267785774330.9</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>22050761.63</t>
+          <t>22050761629670.9</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>21643446.94</t>
+          <t>21643446939893.3</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>20228078.845</t>
+          <t>20228078845331.5</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>14582279.023</t>
+          <t>14582279022982.6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>474052.831</t>
+          <t>474052831459.081</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>462371.5</t>
+          <t>462371500189.989</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>492967.258</t>
+          <t>492967257631.617</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>564479.94</t>
+          <t>564479939946.342</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>542235.914</t>
+          <t>542235914420.17</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>604015.39</t>
+          <t>604015389691.11</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>630327.033</t>
+          <t>630327033156.86</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>711325.261</t>
+          <t>711325260574.008</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>930211.065</t>
+          <t>930211065201.952</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>903202.808</t>
+          <t>903202807580.705</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>930644</t>
+          <t>930643999627.196</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>903004.43</t>
+          <t>903004429680.355</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>880222.566</t>
+          <t>880222566310.213</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>823012.82</t>
+          <t>823012820458.861</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>767814.151</t>
+          <t>767814150789.774</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>934564.781</t>
+          <t>934564781145.307</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>797089.204</t>
+          <t>797089204302.387</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>749910.288</t>
+          <t>749910288283.136</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>856976.92</t>
+          <t>856976920009.371</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>949357.9</t>
+          <t>949357900230.486</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>970340.159</t>
+          <t>970340159269.653</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1040944.263</t>
+          <t>1040944262841.96</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1132666.485</t>
+          <t>1132666484708.92</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1383680.769</t>
+          <t>1383680769106.91</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1292934.771</t>
+          <t>1292934770740.76</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1223278.496</t>
+          <t>1223278496443.07</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1106516.071</t>
+          <t>1106516070582.06</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>970898.519</t>
+          <t>970898519127.776</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>836928.174</t>
+          <t>836928174240.932</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>750093.981</t>
+          <t>750093980844.509</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>10706976.989</t>
+          <t>10706976989425.7</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10538259.16</t>
+          <t>10538259160274.8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>9579678.133</t>
+          <t>9579678133469.64</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>10595437.289</t>
+          <t>10595437288895.4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>11577620.533</t>
+          <t>11577620532911.4</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>12808236.882</t>
+          <t>12808236881912.3</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>12602357.105</t>
+          <t>12602357105169.8</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>13478414.341</t>
+          <t>13478414340505.9</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>16297962.262</t>
+          <t>16297962261603</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>14824494.886</t>
+          <t>14824494886040.4</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>13519145.44</t>
+          <t>13519145440061.1</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>11897618.407</t>
+          <t>11897618406983.8</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>10231113.698</t>
+          <t>10231113697845.3</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>7889173.213</t>
+          <t>7889173213488.82</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>6339957.473</t>
+          <t>6339957473158.06</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3760935.775</t>
+          <t>3760935774973.36</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3876622.359</t>
+          <t>3876622359385</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4411564.078</t>
+          <t>4411564078161.87</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>4971527.628</t>
+          <t>4971527628130.94</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6225798.637</t>
+          <t>6225798637198.39</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6900883.211</t>
+          <t>6900883210558.51</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5267274.518</t>
+          <t>5267274517516.98</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>5154214.356</t>
+          <t>5154214355955.47</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>6486996.539</t>
+          <t>6486996538793.87</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>6674605.28</t>
+          <t>6674605280145</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>7471830.916</t>
+          <t>7471830916046.14</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>6816731.351</t>
+          <t>6816731351222.55</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>6171490.165</t>
+          <t>6171490164593.38</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>5135341.784</t>
+          <t>5135341784179.41</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>4080860.95</t>
+          <t>4080860949630.27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>11201505.572</t>
+          <t>11201505571606.1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10249434.894</t>
+          <t>10249434894379.5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>10491102.625</t>
+          <t>10491102624717.6</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>10404708.92</t>
+          <t>10404708919808</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>12208795.689</t>
+          <t>12208795688820</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>14564030.939</t>
+          <t>14564030939232.4</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>13853747.91</t>
+          <t>13853747909822.3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>13190559.119</t>
+          <t>13190559119172.6</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>13289007.915</t>
+          <t>13289007914996.3</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>11388650.021</t>
+          <t>11388650020897.4</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>11115362.098</t>
+          <t>11115362098079.7</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>9674264.473</t>
+          <t>9674264472878.31</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>7235406.868</t>
+          <t>7235406867806.92</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>5516118.668</t>
+          <t>5516118667641.85</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>4833997.419</t>
+          <t>4833997418985.22</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>330654400.103</t>
+          <t>330654400102551</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>302426375.293</t>
+          <t>302426375293127</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>321383176.24</t>
+          <t>321383176240426</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>379483359.555</t>
+          <t>379483359554653</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>442741488.48</t>
+          <t>442741488479733</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>531208059.249</t>
+          <t>531208059249444</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>572692585.839</t>
+          <t>572692585838755</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>572859807.714</t>
+          <t>572859807714118</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>584043420.939</t>
+          <t>584043420939350</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>492252259.407</t>
+          <t>492252259407407</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>466202689.79</t>
+          <t>466202689790464</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>413531533.649</t>
+          <t>413531533649337</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>319567846.174</t>
+          <t>319567846173543</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>239469461.716</t>
+          <t>239469461715626</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>221355731.815</t>
+          <t>221355731814880</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>133194000.654</t>
+          <t>133194000654146</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>122694666.713</t>
+          <t>122694666713368</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>124330009.919</t>
+          <t>124330009919118</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>132267325.772</t>
+          <t>132267325771937</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>146824326.339</t>
+          <t>146824326338943</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>170432333.504</t>
+          <t>170432333503721</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>176870114.752</t>
+          <t>176870114752224</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>169885784.414</t>
+          <t>169885784413828</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>183815956.573</t>
+          <t>183815956572696</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>169870536.578</t>
+          <t>169870536578383</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>174892744.964</t>
+          <t>174892744963539</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>167293822.224</t>
+          <t>167293822224243</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>142506901.952</t>
+          <t>142506901952339</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>126938547.78</t>
+          <t>126938547780316</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>112745189.397</t>
+          <t>112745189397121</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1224199698.078</t>
+          <t>1224199698078205</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1080294276.538</t>
+          <t>1080294276538341</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1072647755.214</t>
+          <t>1072647755214426</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1185379949.674</t>
+          <t>1185379949673948</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1350080929.429</t>
+          <t>1350080929429389</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1548966367.525</t>
+          <t>1548966367525213</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1608222440.363</t>
+          <t>1608222440363484</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1620551101.992</t>
+          <t>1620551101991687</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1759196168.317</t>
+          <t>1759196168316781</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1564175877.953</t>
+          <t>1564175877953471</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1501206560.297</t>
+          <t>1501206560297307</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>1353913096.398</t>
+          <t>1353913096397593</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>1107867202.976</t>
+          <t>1107867202976497</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>894239014.122</t>
+          <t>894239014121504</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>811982408.231</t>
+          <t>811982408230791</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>abstract_labour.empe.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
